--- a/Zoomlion/ZA20JERT.xlsx
+++ b/Zoomlion/ZA20JERT.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F503"/>
+  <dimension ref="A1:F505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Material No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Item and Spec</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
@@ -1815,7 +1803,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>007736008000011</t>
+          <t>007736008000011 00</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3275,7 +3263,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>007737004000012</t>
+          <t>007737004000012 10</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4241,11 +4229,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Adjustable plate; Pin II</t>
+          <t>Pin II</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4263,21 +4251,21 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>00773700800001090</t>
+          <t>007737008000010 10</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dam-board</t>
+          <t>Adjustable plate</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4289,7 +4277,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>007737008000011</t>
+          <t>00773700800001090</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -4297,13 +4285,13 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Rotary limit support</t>
+          <t>Dam-board</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -4315,15 +4303,15 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>007737008000012</t>
+          <t>007737008000011</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cushion pad; Mounting plate I; Mounting plate</t>
+          <t>Rotary limit support</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -4341,15 +4329,15 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>007737008000016</t>
+          <t>007737008000012</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spacer; Pipeline tray</t>
+          <t>Cushion pad; Mounting plate</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -4367,21 +4355,21 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>00773700810601011</t>
+          <t>007737008000012 21</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bending plate</t>
+          <t>Mounting plate I</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -4393,21 +4381,21 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>00773700810601020</t>
+          <t>007737008000016</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hose seat</t>
+          <t>Spacer; Pipeline tray</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -4419,7 +4407,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>00773700810601031</t>
+          <t>00773700810601011</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -4427,7 +4415,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bending plate I</t>
+          <t>Bending plate</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4445,7 +4433,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>007737008600010</t>
+          <t>00773700810601020</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -4453,13 +4441,13 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Axle I</t>
+          <t>Hose seat</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -4471,7 +4459,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>007737008602000</t>
+          <t>00773700810601031</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -4479,13 +4467,13 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Turntable weldment</t>
+          <t>Bending plate I</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -4497,7 +4485,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>007737008604000</t>
+          <t>007737008600010 81</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4505,7 +4493,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Electric control cabinet bracket II</t>
+          <t>Axle I</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4523,7 +4511,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>007737008606000</t>
+          <t>007737008602000</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4531,7 +4519,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Electric control cabinet</t>
+          <t>Turntable weldment</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4549,7 +4537,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>00773700861001010</t>
+          <t>007737008604000 00</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4557,13 +4545,13 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Dam-board</t>
+          <t>Electric control cabinet bracket II</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard)</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -4575,7 +4563,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>00773700861020000</t>
+          <t>007737008606000</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4583,13 +4571,13 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Centre revolving mounting bracket</t>
+          <t>Electric control cabinet</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard)</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -4601,7 +4589,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>00773700861601050</t>
+          <t>00773700861001010</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4609,13 +4597,13 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Stop lever</t>
+          <t>Dam-board</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -4627,21 +4615,21 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>00773700861601060</t>
+          <t>00773700861020000</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Fixed plate</t>
+          <t>Centre revolving mounting bracket</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -4653,21 +4641,21 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>00773701000001021</t>
+          <t>00773700861601050</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cushion block</t>
+          <t>Stop lever</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Counterweight 00773701040000000</t>
+          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -4679,7 +4667,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>00773701000001040</t>
+          <t>00773700861601060</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4687,13 +4675,13 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Washer</t>
+          <t>Fixed plate</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Counterweight 00773701040000000</t>
+          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -4705,15 +4693,15 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>00773701040001011</t>
+          <t>00773701000001021</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Counterweight block</t>
+          <t>Cushion block</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4731,21 +4719,21 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>00773701100001030</t>
+          <t>00773701000001040</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Adjustable pad</t>
+          <t>Washer</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Counterweight 00773701040000000</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -4757,21 +4745,21 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>00773701120001050</t>
+          <t>00773701040001011</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Door knob bracket</t>
+          <t>Counterweight block</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Counterweight 00773701040000000</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -4783,15 +4771,15 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>00773701130001020</t>
+          <t>00773701100001030</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Left lock seat</t>
+          <t>Adjustable pad</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -4809,15 +4797,15 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>00773701130001040</t>
+          <t>00773701120001050</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Right lock seat</t>
+          <t>Door knob bracket</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -4835,7 +4823,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>00773701130200000</t>
+          <t>00773701130001020</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4843,7 +4831,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Left hood</t>
+          <t>Left lock seat</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4861,7 +4849,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>00773701130400000</t>
+          <t>00773701130001040</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4869,7 +4857,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Right hood</t>
+          <t>Right lock seat</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -4887,7 +4875,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>00773702800001020</t>
+          <t>00773701130200000</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4895,13 +4883,13 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Left hood</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -4913,7 +4901,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>00773702800001021</t>
+          <t>00773701130400000</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4921,13 +4909,13 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Right hood</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -4939,15 +4927,15 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>00773702800001031</t>
+          <t>00773702800001020</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Steering knuckle – Upper wear plate</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4965,7 +4953,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>00773702800001082</t>
+          <t>00773702800001021</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4973,7 +4961,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Frame cover plate</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -4991,15 +4979,15 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>00773702800001100</t>
+          <t>00773702800001031</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Cover plate</t>
+          <t>Steering knuckle – Upper wear plate</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -5017,15 +5005,15 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>00773702800001150</t>
+          <t>00773702800001082</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PinI</t>
+          <t>Frame cover plate</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -5043,15 +5031,15 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>00773702800001200</t>
+          <t>00773702800001100</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Steering  knuckle  –  Lower  wear pad</t>
+          <t>Cover plate</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -5069,7 +5057,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>00773702800001220</t>
+          <t>00773702800001150</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -5077,7 +5065,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Lubrication-free bearing</t>
+          <t>PinI</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -5095,15 +5083,15 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>00773702800001330</t>
+          <t>00773702800001200</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Steering  knuckle  –  Lower  wear pad</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -5121,15 +5109,15 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>00773702800001340</t>
+          <t>00773702800001220</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PinVI</t>
+          <t>Lubrication-free bearing</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -5147,7 +5135,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>00773702800001480</t>
+          <t>00773702800001330</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -5155,7 +5143,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cover plate</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -5173,15 +5161,15 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>00773702800001520</t>
+          <t>00773702800001340</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cover plate</t>
+          <t>PinVI</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -5199,7 +5187,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>00773702800400001</t>
+          <t>00773702800001480</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -5207,7 +5195,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Front axle weldment</t>
+          <t>Cover plate</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -5225,15 +5213,15 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>00773702800800001</t>
+          <t>00773702800001520</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Steering knuckle I</t>
+          <t>Cover plate</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5251,7 +5239,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>00773702801200002</t>
+          <t>00773702800400001</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -5259,7 +5247,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Steering knuckle II</t>
+          <t>Front axle weldment</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5277,15 +5265,15 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>00773702801400000</t>
+          <t>00773702800800001</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Steering cylinder</t>
+          <t>Steering knuckle I</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -5303,7 +5291,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>00773702802000001</t>
+          <t>00773702801200002</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -5311,7 +5299,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Steering linkage</t>
+          <t>Steering knuckle II</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -5329,7 +5317,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>00773702803000001</t>
+          <t>00773702801400000</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -5337,7 +5325,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Float cylinder</t>
+          <t>Steering cylinder</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5355,7 +5343,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>00773702803401010</t>
+          <t>00773702802000001</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -5363,7 +5351,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Motor bracket</t>
+          <t>Steering linkage</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5381,7 +5369,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>00773702803600000</t>
+          <t>00773702803000001</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Motor protective plate</t>
+          <t>Float cylinder</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5407,7 +5395,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>00773702810400001</t>
+          <t>00773702803401010</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -5415,7 +5403,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Fork installation</t>
+          <t>Motor bracket</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5433,21 +5421,21 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>00773705200220011</t>
+          <t>00773702803600000</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Oil tank body</t>
+          <t>Motor protective plate</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -5459,7 +5447,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>00773705200220020</t>
+          <t>00773702810400001</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -5467,13 +5455,13 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Seal pad</t>
+          <t>Fork installation</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -5485,7 +5473,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>00773706200450040</t>
+          <t>00773705200220011</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -5493,13 +5481,13 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Battery positive and negative series wire 4</t>
+          <t>Oil tank body</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -5511,7 +5499,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>00773706200450050</t>
+          <t>00773705200220020</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -5519,13 +5507,13 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Battery  positive terminal  and  manual switch connecting wire</t>
+          <t>Seal pad</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -5537,7 +5525,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>00773706200450060</t>
+          <t>00773706200450040</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -5545,7 +5533,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Manual  switch  and  disk  assembly  fuse connecting wire</t>
+          <t>Battery positive and negative series wire 4</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -5563,15 +5551,15 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>00773706200450080</t>
+          <t>00773706200450050</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No.  5  drive  and  functional  pump  motor connecting wire</t>
+          <t>Battery  positive terminal  and  manual switch connecting wire</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -5589,7 +5577,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>00773706200450090</t>
+          <t>00773706200450060</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -5597,7 +5585,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Emergency battery positive terminal and emergency switch connecting wire</t>
+          <t>Manual  switch  and  disk  assembly  fuse connecting wire</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -5615,15 +5603,15 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>00773706200450100</t>
+          <t>00773706200450080</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Fuse and emergency pump relay connecting wire</t>
+          <t>No.  5  drive  and  functional  pump  motor connecting wire</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -5641,15 +5629,15 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>00773706200450110</t>
+          <t>00773706200450090</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Emergency battery negative terminal and  emergency  pump  relay  connecting wire</t>
+          <t>Emergency battery positive terminal and emergency switch connecting wire</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -5667,7 +5655,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>00773706200450120</t>
+          <t>00773706200450100</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5675,7 +5663,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Rear axle disk assembly negative terminal  and  front  axle  disk  assembly negative terminal connecting wire</t>
+          <t>Fuse and emergency pump relay connecting wire</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -5693,15 +5681,15 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>00773706200450130</t>
+          <t>00773706200450110</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Emergency  switch  and  fuse  connecting wire</t>
+          <t>Emergency battery negative terminal and  emergency  pump  relay  connecting wire</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -5719,7 +5707,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>00775600101801010</t>
+          <t>00773706200450120</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5727,13 +5715,13 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Key cylinder</t>
+          <t>Rear axle disk assembly negative terminal  and  front  axle  disk  assembly negative terminal connecting wire</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -5745,7 +5733,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>00775600101801020</t>
+          <t>00773706200450130</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5753,13 +5741,13 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Emergency  switch  and  fuse  connecting wire</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -5771,7 +5759,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>02551500100210000</t>
+          <t>00775600101801010</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5779,13 +5767,13 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Platform weldment</t>
+          <t>Key cylinder</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Work Platform 00774000120000002 Option</t>
+          <t>Work Platform 00773600100000003 Standard</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -5797,21 +5785,21 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>02564400100401010</t>
+          <t>00775600101801020</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Linkage</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Work Platform 00773600100000003 Standard</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -5823,21 +5811,21 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>02564400100401020</t>
+          <t>02551500100210000</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Platform weldment</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -5849,21 +5837,21 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>02564402802000000</t>
+          <t>02564400100401010</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Angle sensor installation</t>
+          <t>Linkage</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -5875,21 +5863,21 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>02564700300001010</t>
+          <t>02564400100401020</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Luffing balace valve cover plate; Luffing  balace  valve  cover plate</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001; Boom Assembly 02564700400000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -5901,7 +5889,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>02564700300200000</t>
+          <t>02564402802000000</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5909,13 +5897,13 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Base boom</t>
+          <t>Angle sensor installation</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -5927,21 +5915,21 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>02564700300600000</t>
+          <t>02564700300001010</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Telescopic boom sticker</t>
+          <t>Luffing balace valve cover plate; Luffing  balace  valve  cover plate</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Boom Assembly 02564700300000001; Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -5953,7 +5941,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>025647028000010</t>
+          <t>02564700300200000</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5961,13 +5949,13 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Filter bracket</t>
+          <t>Base boom</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -5979,7 +5967,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>02564702800001020</t>
+          <t>02564700300600000</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5987,13 +5975,13 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Charger port protective box</t>
+          <t>Telescopic boom sticker</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -6005,7 +5993,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>02564702800200000</t>
+          <t>025647028000010 40</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -6013,13 +6001,13 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Frame weldment</t>
+          <t>Filter bracket</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -6031,7 +6019,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>02564702800210000</t>
+          <t>02564702800001020</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -6039,7 +6027,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bottom plate</t>
+          <t>Charger port protective box</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -6057,15 +6045,15 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>02564702800400000</t>
+          <t>02564702800200000</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Battery box – Upper cover weldment</t>
+          <t>Frame weldment</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -6083,15 +6071,15 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>02564702810001020</t>
+          <t>02564702800210000</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Steering valve bracket</t>
+          <t>Bottom plate</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -6109,15 +6097,15 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>02564702810001030</t>
+          <t>02564702800400000</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Emergency pump bracket</t>
+          <t>Battery box – Upper cover weldment</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6135,15 +6123,15 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>02564702810800000</t>
+          <t>02564702810001020</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Emergency battery bracket</t>
+          <t>Steering valve bracket</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -6161,7 +6149,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>02564702811200000</t>
+          <t>02564702810001030</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -6169,7 +6157,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Front cover weldment</t>
+          <t>Emergency pump bracket</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -6187,7 +6175,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1010002076</t>
+          <t>02564702810800000</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -6195,13 +6183,13 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Gear pump</t>
+          <t>Emergency battery bracket</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -6213,7 +6201,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1010003029</t>
+          <t>02564702811200000</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -6221,13 +6209,13 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Emergency pump</t>
+          <t>Front cover weldment</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -6239,7 +6227,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1010202248</t>
+          <t>1010002076</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -6247,13 +6235,13 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Rotary actuator</t>
+          <t>Gear pump</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Jib 00773700200000002</t>
+          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -6265,7 +6253,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1010300748</t>
+          <t>1010003029</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -6273,13 +6261,13 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Check valve</t>
+          <t>Emergency pump</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -6291,21 +6279,21 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1010306016</t>
+          <t>1010202248</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Leveling selective valve; Platform select valve</t>
+          <t>Rotary actuator</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Jib 00773700200000002</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -6317,7 +6305,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1010306020</t>
+          <t>1010300748</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -6325,13 +6313,13 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Balance valve</t>
+          <t>Check valve</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
+          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -6343,21 +6331,21 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1010306060</t>
+          <t>1010306016</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Telescopic balance valve</t>
+          <t>Leveling selective valve; Platform select valve</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000</t>
+          <t>Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -6369,7 +6357,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1010306369</t>
+          <t>1010306020</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -6377,13 +6365,13 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Overflow hydraulic lock</t>
+          <t>Balance valve</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000</t>
+          <t>Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -6395,7 +6383,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1010306616</t>
+          <t>1010306060</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -6403,13 +6391,13 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Lifting Balance Valve</t>
+          <t>Telescopic balance valve</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
+          <t>Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -6421,7 +6409,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1010306638</t>
+          <t>1010306369</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -6429,13 +6417,13 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Upper leveling cylinder valve</t>
+          <t>Overflow hydraulic lock</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000</t>
+          <t>Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -6447,7 +6435,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1010306664</t>
+          <t>1010306616</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6455,13 +6443,13 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Check valve</t>
+          <t>Lifting Balance Valve</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -6473,21 +6461,21 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1010306723</t>
+          <t>1010306638</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Left tower boom cylinder control valve; Right tower boom cylinder control valve</t>
+          <t>Upper leveling cylinder valve</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000</t>
+          <t>Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -6499,7 +6487,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1010307351</t>
+          <t>1010306664</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -6507,13 +6495,13 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Steering priority valve</t>
+          <t>Check valve</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000</t>
+          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -6525,21 +6513,21 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1010307371</t>
+          <t>1010306723</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Float CBV</t>
+          <t>Left tower boom cylinder control valve; Right tower boom cylinder control valve</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
+          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -6551,7 +6539,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1010308264</t>
+          <t>1010307351</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -6559,13 +6547,13 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Float control valve</t>
+          <t>Steering priority valve</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -6577,7 +6565,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1010309171</t>
+          <t>1010307371</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -6585,13 +6573,13 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Main valve</t>
+          <t>Float CBV</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -6603,7 +6591,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1010500489</t>
+          <t>1010308264</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -6611,13 +6599,13 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Air Filter</t>
+          <t>Float control valve</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -6629,7 +6617,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1010601138</t>
+          <t>1010309171</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -6637,13 +6625,13 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>High pressure filter</t>
+          <t>Main valve</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000</t>
+          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -6655,7 +6643,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1010601742</t>
+          <t>1010500489</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -6663,7 +6651,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Return-oil filter</t>
+          <t>Air Filter</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6681,7 +6669,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1011200180</t>
+          <t>1010601138</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -6689,13 +6677,13 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Centre revolving connector</t>
+          <t>High pressure filter</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Well-matched Rotary Centre Connector Installation 00773705212200000</t>
+          <t>Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -6707,21 +6695,21 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1019900975</t>
+          <t>1010601742</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Hexagonal socket head plug</t>
+          <t>Return-oil filter</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -6733,7 +6721,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1019901008</t>
+          <t>1011200180</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -6741,13 +6729,13 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Combined connector</t>
+          <t>Centre revolving connector</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Well-matched Rotary Centre Connector Installation 00773705212200000</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -6759,21 +6747,21 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1019901470</t>
+          <t>1019900975</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Liquid-filled thermometer</t>
+          <t>Hexagonal socket head plug</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -6785,7 +6773,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1020005381</t>
+          <t>1019901008</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6793,13 +6781,13 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Motor</t>
+          <t>Combined connector</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -6811,21 +6799,21 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1020103903</t>
+          <t>1019901470</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Liquid-filled thermometer</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -6837,21 +6825,21 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1020103955</t>
+          <t>1020005381</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Connector assembly</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -6863,21 +6851,21 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1020201651</t>
+          <t>1020103903</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -6889,21 +6877,21 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1020202051</t>
+          <t>1020103955</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DC-DC converter</t>
+          <t>Connector assembly</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -6915,7 +6903,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1020304559</t>
+          <t>1020201651</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6923,14 +6911,10 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Light relay</t>
-        </is>
-      </c>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
@@ -6945,7 +6929,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1020304584</t>
+          <t>1020202051</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6953,13 +6937,13 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Power relay</t>
+          <t>DC-DC converter</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -6971,7 +6955,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1020304982</t>
+          <t>1020304559</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6979,13 +6963,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Alarm buzzer</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Relay</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Light relay</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -6997,7 +6985,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1020404399</t>
+          <t>1020304584</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -7005,13 +6993,13 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Work alarm light</t>
+          <t>Power relay</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -7023,7 +7011,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1020404405</t>
+          <t>1020304982</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -7031,13 +7019,13 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Flash buzzer</t>
+          <t>Alarm buzzer</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Turntable cables00773706200410001</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -7049,7 +7037,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1020405061</t>
+          <t>1020404399</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -7057,13 +7045,13 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Alarm indicator panel</t>
+          <t>Work alarm light</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Turntable cables00773706200410001</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -7075,21 +7063,21 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1020509007</t>
+          <t>1020404405</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Button seat</t>
+          <t>Flash buzzer</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -7101,21 +7089,21 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1020516032</t>
+          <t>1020405061</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Tower boom stowed limit switch - right; Boom length limit switch 1; Boom length limit switch 2</t>
+          <t>Alarm indicator panel</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001; Boom Cables 00773706210430001</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -7127,7 +7115,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1020519658</t>
+          <t>1020509007</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -7135,14 +7123,10 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Emergency stop button</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Emergency stop switch</t>
-        </is>
-      </c>
+          <t>Button seat</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
@@ -7157,25 +7141,21 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1020520084</t>
+          <t>1020516032</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Platform rotation; Platform leveling; Jib lifting; Boom extension; Boom lifting; Tower boom lifting; Turntable rotation; Emergency power and enable; Platform rotation switch; Jib lifting switch</t>
-        </is>
-      </c>
+          <t>Tower boom stowed limit switch - right; Boom length limit switch 1; Boom length limit switch 2</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Turntable cables00773706200410001; Boom Cables 00773706210430001</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -7187,21 +7167,25 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1020520943</t>
+          <t>1020519658</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Key switch</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>Emergency stop button</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Emergency stop switch</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -7213,21 +7197,25 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1020520993</t>
+          <t>1020520084</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Handle</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Toggle switch</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Platform rotation; Platform leveling; Jib lifting; Boom extension; Boom lifting; Tower boom lifting; Turntable rotation; Emergency power and enable; Platform rotation switch; Jib lifting switch</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -7239,7 +7227,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1020520994</t>
+          <t>1020520943</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -7247,13 +7235,13 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Handle</t>
+          <t>Key switch</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -7265,7 +7253,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1020520995</t>
+          <t>1020520993</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -7273,7 +7261,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Potentiometer</t>
+          <t>Handle</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -7291,21 +7279,21 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1020520996</t>
+          <t>1020520994</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Emergency switch</t>
+          <t>Handle</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000; Chassis Cables 00773706200420000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -7317,7 +7305,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1020521022</t>
+          <t>1020520995</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -7325,13 +7313,13 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Foot switch</t>
+          <t>Potentiometer</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -7343,25 +7331,21 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1020521443</t>
+          <t>1020520996</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Joystick</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Travel speed control</t>
-        </is>
-      </c>
+          <t>Emergency switch</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Power wire 00773706200450000; Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -7373,7 +7357,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1020521444</t>
+          <t>1020521022</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -7381,17 +7365,13 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Joystick</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+          <t>Foot switch</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -7403,7 +7383,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1020521445</t>
+          <t>1020521443</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -7416,7 +7396,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Platform leveling</t>
+          <t>Travel speed control</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -7433,7 +7413,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1020604246</t>
+          <t>1020521444</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -7441,13 +7421,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Fuse holder</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Joystick</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -7459,21 +7443,25 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1020604934</t>
+          <t>1020521445</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Joystick</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Platform leveling</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -7485,25 +7473,21 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1020700440</t>
+          <t>1020604246</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>Slip ring plug 2</t>
-        </is>
-      </c>
+          <t>Fuse holder</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001; Chassis Cables 00773706200420000</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -7515,21 +7499,21 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1020700540</t>
+          <t>1020604934</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Terminal resistance</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Boom Cables 00773706210430001</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -7541,20 +7525,20 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1020700942</t>
+          <t>1020700440</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Sheath; Connector</t>
+          <t>Sheath</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Plug-in</t>
+          <t>Slip ring plug 2</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7571,7 +7555,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1020700949</t>
+          <t>1020700540</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -7579,13 +7563,13 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Sheath</t>
+          <t>Terminal resistance</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Boom Cables 00773706210430001</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -7597,25 +7581,25 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1020700951</t>
+          <t>1020700942</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Connector; Sheath</t>
+          <t>Sheath; Connector</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Leveling select valve; Main boom retracting valve; Turntable left turn valve; Rotary reversing valve 2; Rotary reversing valve 1; Turntable right-turn valve; Main boom extending valve; Tower boom lifting valve; Main boom lifting valve; Light- reserved; Main boom lowering valve; Jib lifting select valve</t>
+          <t>Plug-in</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001; Boom Cables 00773706210430001; Chassis Cables 00773706200420000; Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
+          <t>Turntable cables00773706200410001; Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -7627,25 +7611,21 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1020700957</t>
+          <t>1020700949</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
           <t>Sheath</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Plug-in</t>
-        </is>
-      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001; Chassis Cables 00773706200420000</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -7657,21 +7637,25 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1020700961</t>
+          <t>1020700951</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Connector; Sheath</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Leveling select valve; Main boom retracting valve; Turntable left turn valve; Rotary reversing valve 2; Rotary reversing valve 1; Turntable right-turn valve; Main boom extending valve; Tower boom lifting valve; Main boom lifting valve; Light- reserved; Main boom lowering valve; Jib lifting select valve</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Turntable cables00773706200410001; Boom Cables 00773706210430001; Chassis Cables 00773706200420000; Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -7683,21 +7667,25 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1020700969</t>
+          <t>1020700957</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Angle limit switch - inside</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Plug-in</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001</t>
+          <t>Turntable cables00773706200410001; Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -7709,7 +7697,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1020702062</t>
+          <t>1020700961</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -7735,25 +7723,21 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1020703391</t>
+          <t>1020700969</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Slip ring plug 1</t>
-        </is>
-      </c>
+          <t>Angle limit switch - inside</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001; Chassis Cables 00773706200420000</t>
+          <t>Turntable cables00773706200410001</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -7765,7 +7749,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1020703393</t>
+          <t>1020702062</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -7773,17 +7757,13 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Round connector</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Platform cables</t>
-        </is>
-      </c>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -7795,25 +7775,25 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1020703394</t>
+          <t>1020703391</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Deutsch connector; Angle limit switch - outside; Connector</t>
+          <t>Sheath</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Chain cables</t>
+          <t>Slip ring plug 1</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000; Turntable cables00773706200410001; Boom Cables 00773706210430001</t>
+          <t>Turntable cables00773706200410001; Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -7825,7 +7805,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1020703635</t>
+          <t>1020703393</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -7833,17 +7813,17 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Sheath</t>
+          <t>Round connector</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Functional pump temperature plug</t>
+          <t>Platform cables</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -7855,7 +7835,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1020704265</t>
+          <t>1020703394</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -7863,13 +7843,17 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Earth terminal row</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Deutsch connector; Angle limit switch - outside; Connector</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Chain cables</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000; Turntable cables00773706200410001; Boom Cables 00773706210430001</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -7881,21 +7865,25 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1020705826</t>
+          <t>1020703635</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Diode terminal</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Functional pump temperature plug</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -7907,25 +7895,21 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1020810958</t>
+          <t>1020704265</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Joystick</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Emergency power and enable; Drive orientation</t>
-        </is>
-      </c>
+          <t>Earth terminal row</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -7937,21 +7921,21 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1020903393</t>
+          <t>1020705826</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>On-board charger</t>
+          <t>Diode terminal</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -7963,21 +7947,25 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1020903396</t>
+          <t>1020810958</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Emergency battery</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
+          <t>Joystick</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Emergency power and enable; Drive orientation</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -7989,7 +7977,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1020999074</t>
+          <t>1020903393</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7997,7 +7985,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>On-board charger</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -8015,21 +8003,21 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1020999139</t>
+          <t>1020903396</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Emergency battery</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -8041,7 +8029,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1021404016</t>
+          <t>1020999074</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -8049,13 +8037,13 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Load cell</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -8067,21 +8055,21 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1021404018</t>
+          <t>1020999139</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Frame angle sensor</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -8093,7 +8081,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1021404019</t>
+          <t>1021404016</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -8101,13 +8089,13 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Boom leveling angle sensor</t>
+          <t>Load cell</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Boom Cables 00773706210430001</t>
+          <t>Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -8119,7 +8107,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1022200446</t>
+          <t>1021404018</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -8127,17 +8115,13 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Platform connector</t>
-        </is>
-      </c>
+          <t>Frame angle sensor</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -8149,7 +8133,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1022397102</t>
+          <t>1021404019</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -8157,13 +8141,13 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Open bellows</t>
+          <t>Boom leveling angle sensor</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Work Platform 00774000120000002 Option</t>
+          <t>Boom Cables 00773706210430001</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -8175,7 +8159,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1022397103</t>
+          <t>1022200446</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -8183,13 +8167,17 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Open bellows</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Platform connector</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard</t>
+          <t>Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -8201,7 +8189,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1022399012</t>
+          <t>1022397102</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -8209,13 +8197,13 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Line slot</t>
+          <t>Open bellows</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -8227,7 +8215,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1029801230</t>
+          <t>1022397103</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -8235,17 +8223,13 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Functional pump speed plug</t>
-        </is>
-      </c>
+          <t>Open bellows</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Work Platform 00773600100000003 Standard</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -8257,15 +8241,15 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1029802085</t>
+          <t>1022399012</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Nylon plug</t>
+          <t>Line slot</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -8283,21 +8267,25 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1029804205</t>
+          <t>1029801230</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Jam nut</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Functional pump speed plug</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -8309,21 +8297,21 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1029805416</t>
+          <t>1029802085</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Slip ring</t>
+          <t>Nylon plug</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -8335,25 +8323,21 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1029900318</t>
+          <t>1029804205</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Left steering valve; Right steering valve</t>
-        </is>
-      </c>
+          <t>Jam nut</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -8365,7 +8349,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1029900667</t>
+          <t>1029805416</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -8373,13 +8357,13 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Main power switch</t>
+          <t>Slip ring</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Turntable cables00773706200410001</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -8391,21 +8375,25 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1029902630</t>
+          <t>1029900318</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Left steering valve; Right steering valve</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -8417,21 +8405,21 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1029902632</t>
+          <t>1029900667</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Main power switch</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -8443,25 +8431,21 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1029902634</t>
+          <t>1029902630</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>32 core sheath</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>Turntable cables</t>
-        </is>
-      </c>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Turntable cables00773706200410001</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -8473,15 +8457,15 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1029902635</t>
+          <t>1029902632</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Sheath</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -8499,7 +8483,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1029903316</t>
+          <t>1029902634</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -8507,13 +8491,17 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>32 core sheath</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Turntable cables</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Turntable cables00773706200410001</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -8525,7 +8513,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1029903317</t>
+          <t>1029902635</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -8533,17 +8521,13 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>48 core sheath</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>Turntable cables</t>
-        </is>
-      </c>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
+          <t>Turntable cables00773706200410001</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -8555,25 +8539,21 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1029903711</t>
+          <t>1029903316</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Connector; Sheath</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>Chain - upper plug; Chain lower plug</t>
-        </is>
-      </c>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Boom Cables 00773706210430001; Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
+          <t>Turntable cables00773706200410001</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -8585,25 +8565,25 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1029904911</t>
+          <t>1029903317</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Spring washer 5; Washer 5-200HV</t>
+          <t>48 core sheath</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>GB93</t>
+          <t>Turntable cables</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -8615,21 +8595,25 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1029904980</t>
+          <t>1029903711</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Connector; Sheath</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Chain - upper plug; Chain lower plug</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Boom Cables 00773706210430001; Platform cables 00773706200440001 Chain Cables Change 00773706200610000</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -8641,21 +8625,25 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1029905392</t>
+          <t>1029904911</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>Spring washer 5; Washer 5-200HV</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>GB93</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
+          <t>Work Platform 00773600100000003 Standard; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -8667,21 +8655,21 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1029907231</t>
+          <t>1029904980</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Fine slip ring</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Chassis Cables 00773706200420000</t>
+          <t>Turntable Electric Cabinet Assembly 00773706200220001; Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -8693,21 +8681,21 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1029909496</t>
+          <t>1029905392</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Drive front axle assembly</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Platform Electric Cabinet Assembly 00773706200210000</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -8719,7 +8707,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1029909497</t>
+          <t>1029907231</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -8727,13 +8715,13 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Drive rear axle assembly</t>
+          <t>Fine slip ring</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Power wire 00773706200450000</t>
+          <t>Chassis Cables 00773706200420000</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -8745,7 +8733,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1030202348</t>
+          <t>1029909496</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -8753,13 +8741,13 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Rotary reducer</t>
+          <t>Drive front axle assembly</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Rotary Mechanism 00773700900000000</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -8771,21 +8759,21 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1030203018</t>
+          <t>1029909497</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Reducer motor assembly</t>
+          <t>Drive rear axle assembly</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Power wire 00773706200450000</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -8797,21 +8785,21 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1030800695</t>
+          <t>1030202348</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Tire</t>
+          <t>Rotary reducer</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Rotary Mechanism 00773700900000000</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -8823,15 +8811,15 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1030800696</t>
+          <t>1030203018</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Tire</t>
+          <t>Reducer motor assembly</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -8849,7 +8837,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1030801255</t>
+          <t>1030800695</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -8875,7 +8863,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1030801256</t>
+          <t>1030800696</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -8901,25 +8889,21 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1040000135</t>
+          <t>1030801255</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Bolt M8×55-8.8</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>GB/T5783</t>
-        </is>
-      </c>
+          <t>Tire</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -8931,25 +8915,21 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1040000289</t>
+          <t>1030801256</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Bolt M6×50-8.8; M6×50-8.8</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>GB/T5783; GB/T5783-2000</t>
-        </is>
-      </c>
+          <t>Tire</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002; Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -8961,21 +8941,25 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1040000574</t>
+          <t>1040000135</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Bolt M10×30-10.9</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Bolt M8×55-8.8</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Boom Assembly 02564700400000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -8987,25 +8971,25 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1040001631</t>
+          <t>1040000289</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Bolt M6×20-A2-70</t>
+          <t>Bolt M6×50-8.8; M6×50-8.8</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5783; GB/T5783-2000</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000; Chassis 02564702800000002</t>
+          <t>Chassis 02564702800000002; Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -9017,22 +9001,18 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1040001640</t>
+          <t>1040000574</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Bolt M6×25-A2-70</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>GB/T5783</t>
-        </is>
-      </c>
+          <t>Bolt M10×30-10.9</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>Boom Assembly 02564700300000001</t>
@@ -9047,25 +9027,25 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1040001703</t>
+          <t>1040001631</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Bolt M12×65-10.9</t>
+          <t>Bolt M6×20-A2-70</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Anti-crushing device 00771600122300000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -9077,15 +9057,15 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1040001715</t>
+          <t>1040001640</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Bolt M6×45-A2-70</t>
+          <t>Bolt M6×25-A2-70</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9095,7 +9075,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -9107,25 +9087,25 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1040002433</t>
+          <t>1040001703</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Bolt M10×20-8.8</t>
+          <t>Bolt M12×65-10.9</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Jib 00773700200000002; Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -9137,7 +9117,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1040002435</t>
+          <t>1040001715</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -9145,7 +9125,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Bolt M10×35-8.8</t>
+          <t>Bolt M6×45-A2-70</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9167,15 +9147,15 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1040002436</t>
+          <t>1040002433</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Bolt M12×25-8.8</t>
+          <t>Bolt M10×20-8.8</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9185,7 +9165,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000</t>
+          <t>Jib 00773700200000002; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -9197,15 +9177,15 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1040002437</t>
+          <t>1040002435</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Bolt M12×35-8.8</t>
+          <t>Bolt M10×35-8.8</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9215,7 +9195,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -9227,15 +9207,15 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1040002445</t>
+          <t>1040002436</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Bolt M16×35-8.8</t>
+          <t>Bolt M12×25-8.8</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9257,15 +9237,15 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1040002446</t>
+          <t>1040002437</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Bolt M16×40-8.8</t>
+          <t>Bolt M12×35-8.8</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9275,7 +9255,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000; Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -9287,15 +9267,15 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1040002555</t>
+          <t>1040002445</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Bolt M6×16-A2-70</t>
+          <t>Bolt M16×35-8.8</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9305,7 +9285,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000</t>
+          <t>Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -9317,15 +9297,15 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040002555 </t>
+          <t>1040002446</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Bolt M6×16-A2-70</t>
+          <t>Bolt M16×40-8.8</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9335,7 +9315,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Boom Assembly 02564700400000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -9347,15 +9327,15 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1040002738</t>
+          <t>1040002555</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Bolt M6×12-A2-70</t>
+          <t>Bolt M6×16-A2-70</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9365,7 +9345,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001; Turntable 0773700860000000</t>
+          <t>Anti-crushing device 00771600122300000</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -9377,7 +9357,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040003324 </t>
+          <t>1040002555 50</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -9385,7 +9365,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Bolt M16×30-10.9-DKL</t>
+          <t>Bolt M6×16-A2-70</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9407,15 +9387,15 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1040003572</t>
+          <t>1040002738</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Bolt M20×55-10.9-DKL</t>
+          <t>Bolt M6×12-A2-70</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9425,7 +9405,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700300000001; Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -9437,7 +9417,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1040004029</t>
+          <t>1040003324 10</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -9445,7 +9425,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Bolt M12×35-10.9</t>
+          <t>Bolt M16×30-10.9-DKL</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9455,7 +9435,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -9467,15 +9447,15 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1040004032</t>
+          <t>1040003572</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bolt M10×20-8.8; Bolt</t>
+          <t>Bolt M20×55-10.9-DKL</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9485,7 +9465,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -9497,21 +9477,25 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040004032 </t>
+          <t>1040004029</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bolt</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>Bolt M12×35-10.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -9523,15 +9507,15 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1040004033</t>
+          <t>1040004032</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Bolt M10×25-10.9</t>
+          <t>Bolt M10×20-8.8; Bolt</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9541,7 +9525,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Boom Assembly 02564700300000001; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -9553,22 +9537,18 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040004033 </t>
+          <t>1040004032 91</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bolt M10×25-10.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>GB/T5783</t>
-        </is>
-      </c>
+          <t>Bolt</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>Turntable 0773700860000000</t>
@@ -9583,15 +9563,15 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1040004499</t>
+          <t>1040004033</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Bolt M20×45-8.8</t>
+          <t>Bolt M10×25-10.9</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9601,7 +9581,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -9613,15 +9593,15 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1040004508</t>
+          <t>1040004033 01</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Bolt M10×45-8.8</t>
+          <t>Bolt M10×25-10.9</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9631,7 +9611,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -9643,15 +9623,15 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1040004511</t>
+          <t>1040004499</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Bolt M12×30-8.8</t>
+          <t>Bolt M20×45-8.8</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9661,7 +9641,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -9673,15 +9653,15 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1040004517</t>
+          <t>1040004508</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Bolt M8×16-8.8</t>
+          <t>Bolt M10×45-8.8</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9691,7 +9671,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Jib 00773700200000002; Boom Assembly 02564700400000000; Hood 00773701130000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -9703,7 +9683,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1040004518</t>
+          <t>1040004511</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -9711,7 +9691,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Bolt M8×20-8.8</t>
+          <t>Bolt M12×30-8.8</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9721,7 +9701,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -9733,15 +9713,15 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040004518 </t>
+          <t>1040004517</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Bolt M8×20-8.8</t>
+          <t>Bolt M8×16-8.8</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9751,7 +9731,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Jib 00773700200000002; Boom Assembly 02564700400000000; Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -9763,15 +9743,15 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1040004519</t>
+          <t>1040004518</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Bolt M8×25-8.8</t>
+          <t>Bolt M8×20-8.8</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9781,7 +9761,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Chain System 00773700700000001; Turntable 0773700860000000; Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -9793,15 +9773,15 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1040004520</t>
+          <t>1040004518 00</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Bolt M8×30-8.8</t>
+          <t>Bolt M8×20-8.8</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9811,7 +9791,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001; Turntable 0773700860000000; Hood 00773701130000000; Chassis 02564702800000002</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -9823,15 +9803,15 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1040004521</t>
+          <t>1040004519</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Bolt M8×45-8.8</t>
+          <t>Bolt M8×25-8.8</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9841,7 +9821,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Chain System 00773700700000001; Turntable 0773700860000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -9853,15 +9833,15 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1040004522</t>
+          <t>1040004520</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Bolt M8×50-8.8</t>
+          <t>Bolt M8×30-8.8</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9871,7 +9851,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Boom Assembly 02564700400000000</t>
+          <t>Boom Assembly 02564700300000001; Turntable 0773700860000000; Hood 00773701130000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -9883,25 +9863,25 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1040004535</t>
+          <t>1040004521</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Bolt M10×60-8.8</t>
+          <t>Bolt M8×45-8.8</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -9913,15 +9893,15 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1040004553</t>
+          <t>1040004522</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Bolt M6×35-8.8</t>
+          <t>Bolt M8×50-8.8</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -9931,7 +9911,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Work Platform 00773600100000003 Standard; Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -9943,25 +9923,25 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1040004556</t>
+          <t>1040004535</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Bolt M12×35-8.8</t>
+          <t>Bolt M10×60-8.8</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>GB/T16674.1</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -9973,25 +9953,25 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1040004557</t>
+          <t>1040004553</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Bolt M8×50-8.8</t>
+          <t>Bolt M6×35-8.8</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>GB/T16674.1</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Chain System 00773700700000001</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -10003,25 +9983,25 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1040004565</t>
+          <t>1040004556</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Bolt M10×30-8.8-DKL</t>
+          <t>Bolt M12×35-8.8</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T16674.1</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000; Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -10033,7 +10013,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1040004603</t>
+          <t>1040004557</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -10041,12 +10021,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Bolt M8×75-8.8</t>
+          <t>Bolt M8×50-8.8</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T16674.1</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10063,25 +10043,25 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1040004613</t>
+          <t>1040004565</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Bolt M24×60-10.9</t>
+          <t>Bolt M10×30-8.8-DKL</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Counterweight 00773701040000000</t>
+          <t>Hood 00773701130000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -10093,25 +10073,25 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1040004619</t>
+          <t>1040004603</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Bolt M8×35-8.8</t>
+          <t>Bolt M8×75-8.8</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Jib 00773700200000002</t>
+          <t>Chain System 00773700700000001</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -10123,25 +10103,25 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1040004646</t>
+          <t>1040004613</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Bolt M10×15-8.8; BoltM10×15-8.8</t>
+          <t>Bolt M24×60-10.9</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
+          <t>Counterweight 00773701040000000</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -10153,25 +10133,25 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1040004648</t>
+          <t>1040004619</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Bolt M16×90-10.9</t>
+          <t>Bolt M8×35-8.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>GB/T1228</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Rotary Mechanism 00773700900000000</t>
+          <t>Jib 00773700200000002</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -10183,15 +10163,15 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1040004672</t>
+          <t>1040004646</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Bolt M5×10-8.8</t>
+          <t>Bolt M10×15-8.8; BoltM10×15-8.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10201,7 +10181,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Boom Assembly 02564700400000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -10213,21 +10193,25 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1040004678</t>
+          <t>1040004648</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Door knob bolt</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
+          <t>Bolt M16×90-10.9</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>GB/T1228</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Rotary Mechanism 00773700900000000</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -10239,15 +10223,15 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1040005681</t>
+          <t>1040004672</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Hexagon head bolt M16×65-8.8</t>
+          <t>Bolt M5×10-8.8</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10257,7 +10241,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -10269,25 +10253,21 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1040005840</t>
+          <t>1040004678</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bolt M16×100-10.9</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>GB/T1228</t>
-        </is>
-      </c>
+          <t>Door knob bolt</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Rotary Mechanism 00773700900000000</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -10299,15 +10279,15 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1040005844</t>
+          <t>1040005681</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Bolt M6×10-A2-70</t>
+          <t>Hexagon head bolt M16×65-8.8</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10317,7 +10297,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Boom Assembly 02564700300000001</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -10329,25 +10309,25 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1040005845</t>
+          <t>1040005840</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Bolt M10×65-8.8</t>
+          <t>Bolt M16×100-10.9</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T1228</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard)</t>
+          <t>Rotary Mechanism 00773700900000000</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -10359,25 +10339,25 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1040005852</t>
+          <t>1040005844</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Bolt M12×20-8.8</t>
+          <t>Bolt M6×10-A2-70</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>GB/T5787</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -10389,21 +10369,25 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1040006017</t>
+          <t>1040005845</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Screw    M6×25-A2-70; Screw M6×25-A2-70</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>Bolt M10×65-8.8</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard)</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -10415,21 +10399,25 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1040006458</t>
+          <t>1040005852</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Strengthen cup head bolt M12×50-8.8 (Full thread)</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr"/>
+          <t>Bolt M12×20-8.8</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>GB/T5787</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -10441,21 +10429,21 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1040006550</t>
+          <t>1040006017</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Bolt M16×40-10.9</t>
+          <t>Screw    M6×25-A2-70; Screw M6×25-A2-70</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -10467,7 +10455,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040007536 </t>
+          <t>1040006458</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -10475,13 +10463,13 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>bracket I</t>
+          <t>Strengthen cup head bolt M12×50-8.8 (Full thread)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -10493,25 +10481,21 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1040007563</t>
+          <t>1040006550</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Bolt M24×290-10.9</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>GB/T5782</t>
-        </is>
-      </c>
+          <t>Bolt M16×40-10.9</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -10523,25 +10507,21 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1040100105</t>
+          <t>1040007536 00</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Screw M6×25-8.8</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>GB/T70.1</t>
-        </is>
-      </c>
+          <t>bracket I</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -10553,25 +10533,25 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1040100148</t>
+          <t>1040007563</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>ScrewM8×45-8.8</t>
+          <t>Bolt M24×290-10.9</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -10583,15 +10563,15 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1040100438</t>
+          <t>1040100105</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Screw M5×55-8.8</t>
+          <t>Screw M6×25-8.8</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10601,7 +10581,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -10613,25 +10593,25 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040100714 </t>
+          <t>1040100148</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Screw M12×130-8.8</t>
+          <t>ScrewM8×45-8.8</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -10643,15 +10623,15 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1040101412</t>
+          <t>1040100438</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>ScrewM8×50</t>
+          <t>Screw M5×55-8.8</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -10661,7 +10641,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000</t>
+          <t>Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -10673,15 +10653,15 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1040101492</t>
+          <t>1040100714 81</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Screw M10×25-8.8</t>
+          <t>Screw M12×130-8.8</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10691,7 +10671,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000; Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Well-matched Rotary Centre Connector Installation 00773705212200000</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -10703,7 +10683,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1040101643</t>
+          <t>1040101412</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -10711,7 +10691,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>ScrewM6×30-A2-70</t>
+          <t>ScrewM8×50</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10721,7 +10701,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -10733,15 +10713,15 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1040101978</t>
+          <t>1040101492</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Screw M12×30-10.9</t>
+          <t>Screw M10×25-8.8</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -10751,7 +10731,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Boom Assembly 02564700400000000; Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Well-matched Rotary Centre Connector Installation 00773705212200000</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -10763,15 +10743,15 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040102040 </t>
+          <t>1040101643</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Screw M10×40-10.9</t>
+          <t>ScrewM6×30-A2-70</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10781,7 +10761,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -10793,15 +10773,15 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1040102372</t>
+          <t>1040101978</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Hexagon socket cap screw M6×20-A2-70</t>
+          <t>Screw M12×30-10.9</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10823,21 +10803,25 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1040102429</t>
+          <t>1040102040 91</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Screw</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>Screw M10×40-10.9</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>GB/T70.1</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -10849,15 +10833,15 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1040102737</t>
+          <t>1040102372</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Screw M8×30-8.8</t>
+          <t>Hexagon socket cap screw M6×20-A2-70</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10867,7 +10851,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Chain System 00773700700000001; Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -10879,25 +10863,21 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1040102738</t>
+          <t>1040102429</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Screw M8×55-8.8</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>GB/T70.1</t>
-        </is>
-      </c>
+          <t>Screw</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -10909,15 +10889,15 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1040102739</t>
+          <t>1040102737</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Screw M8×60-8.8</t>
+          <t>Screw M8×30-8.8</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10927,7 +10907,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
+          <t>Chain System 00773700700000001; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -10939,15 +10919,15 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1040102751</t>
+          <t>1040102738</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Screw M5×25-8.8</t>
+          <t>Screw M8×55-8.8</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -10957,7 +10937,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Chain System 00773700700000001</t>
+          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -10969,15 +10949,15 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1040102776</t>
+          <t>1040102739</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Screw M4×35-8.8</t>
+          <t>Screw M8×60-8.8</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -10987,7 +10967,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000</t>
+          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -10999,15 +10979,15 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1040102778</t>
+          <t>1040102751</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Screw M6×10-8.8</t>
+          <t>Screw M5×25-8.8</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11017,7 +10997,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Chain System 00773700700000001</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -11029,25 +11009,25 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1040103076</t>
+          <t>1040102776</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Screw M8×16-8.8</t>
+          <t>Screw M4×35-8.8</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>GB/T70.3</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Jib 00773700200000002; Boom Assembly 02564700300000001; Chain System 00773700700000001; Boom Assembly 02564700400000000</t>
+          <t>Anti-crushing device 00771600122300000</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -11059,15 +11039,15 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1040103108</t>
+          <t>1040102778</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Screw M5×50-8.8</t>
+          <t>Screw M6×10-8.8</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11077,7 +11057,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -11089,11 +11069,11 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1040103111</t>
+          <t>1040103076</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -11102,12 +11082,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T70.3</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000</t>
+          <t>Jib 00773700200000002; Boom Assembly 02564700300000001; Chain System 00773700700000001; Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -11119,15 +11099,15 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1040103112</t>
+          <t>1040103108</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Screw    M8×25-8.8; Screw M8×25-8.8</t>
+          <t>Screw M5×50-8.8</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11137,7 +11117,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -11149,15 +11129,15 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1040103114</t>
+          <t>1040103111</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ScrewM8×45-8.8</t>
+          <t>Screw M8×16-8.8</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11167,7 +11147,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -11179,25 +11159,25 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1040103123</t>
+          <t>1040103112</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Screw M6×30-A2-70</t>
+          <t>Screw    M8×25-8.8; Screw M8×25-8.8</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>GB/T70.2</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -11209,21 +11189,25 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1040103133</t>
+          <t>1040103114</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Screw M6×30-A2-70</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr"/>
+          <t>ScrewM8×45-8.8</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>GB/T70.1</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Jib 00773700200000002; Boom Assembly 02564700300000001</t>
+          <t>Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -11235,21 +11219,25 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1040103140</t>
+          <t>1040103123</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Screw M12×25-8.8</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr"/>
+          <t>Screw M6×30-A2-70</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>GB/T70.2</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000</t>
+          <t>Anti-crushing device 00771600122300000</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -11261,25 +11249,21 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1040103164</t>
+          <t>1040103133</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Screw M10×30-8.8</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>GB/T70.3</t>
-        </is>
-      </c>
+          <t>Screw M6×30-A2-70</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000</t>
+          <t>Jib 00773700200000002; Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -11291,21 +11275,21 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1040103166</t>
+          <t>1040103140</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Screw</t>
+          <t>Screw M12×25-8.8</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -11317,21 +11301,25 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1040103173</t>
+          <t>1040103164</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Screw    M6×50-8.8</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr"/>
+          <t>Screw M10×30-8.8</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>GB/T70.3</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard</t>
+          <t>Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -11343,22 +11331,18 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1040103558</t>
+          <t>1040103166</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Screw M8×25-8.8</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>GB/T70.3</t>
-        </is>
-      </c>
+          <t>Screw</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>Chassis 02564702800000002</t>
@@ -11373,25 +11357,21 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040103558 </t>
+          <t>1040103173</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Screw M8×25-8.8</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>GB/T70.3</t>
-        </is>
-      </c>
+          <t>Screw    M6×50-8.8</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Work Platform 00773600100000003 Standard</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -11403,7 +11383,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1040103731</t>
+          <t>1040103558</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -11411,7 +11391,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Screw M10×25-10.9</t>
+          <t>Screw M8×25-8.8</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -11421,7 +11401,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Counterweight 00773701040000000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -11433,25 +11413,25 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1040200113</t>
+          <t>1040103558 90</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>NutM10-8; Nut M10-8</t>
+          <t>Screw M8×25-8.8</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T70.3</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard); Hood 00773701130000000; Chassis 02564702800000002</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -11463,25 +11443,25 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1040200503</t>
+          <t>1040103731</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Nut M8-8; Nut M8</t>
+          <t>Screw M10×25-10.9</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T70.3</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chain System 00773700700000001; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Hood 00773701130000000; Chassis 02564702800000002; Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000</t>
+          <t>Counterweight 00773701040000000</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -11493,25 +11473,25 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1040200504</t>
+          <t>1040200113</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Nut M10-8</t>
+          <t>NutM10-8; Nut M10-8</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Hood 00773701130000000</t>
+          <t>Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard); Hood 00773701130000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -11523,15 +11503,15 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1040200507</t>
+          <t>1040200503</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Nut M12-8</t>
+          <t>Nut M8-8; Nut M8</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -11541,7 +11521,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chain System 00773700700000001; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Hood 00773701130000000; Chassis 02564702800000002; Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -11553,7 +11533,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1040200669</t>
+          <t>1040200504</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -11561,17 +11541,17 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Nut M12</t>
+          <t>Nut M10-8</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>GB/T13681</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -11583,25 +11563,25 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1040201089</t>
+          <t>1040200507</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Nut M8-8</t>
+          <t>Nut M12-8</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000; Hood 00773701130000000; Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -11613,20 +11593,20 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1040201111</t>
+          <t>1040200669</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Nut M24-10</t>
+          <t>Nut M12</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>GB/T889</t>
+          <t>GB/T13681</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -11643,25 +11623,25 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1040201163</t>
+          <t>1040201089</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Nut M12-10</t>
+          <t>Nut M8-8</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Turntable 0773700860000000; Hood 00773701130000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -11673,7 +11653,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1040201381</t>
+          <t>1040201111</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -11681,12 +11661,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Nut M12-8</t>
+          <t>Nut M24-10</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T889</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -11703,25 +11683,25 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1040201772</t>
+          <t>1040201163</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Nut M4-A2-70; NutM4-A2-70</t>
+          <t>Nut M12-10</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000; Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -11733,21 +11713,25 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1040201860</t>
+          <t>1040201381</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Nut</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr"/>
+          <t>Nut M12-8</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>GB/T6170</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -11759,25 +11743,25 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1040201896</t>
+          <t>1040201772</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Nut M6-8</t>
+          <t>Nut M4-A2-70; NutM4-A2-70</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Anti-crushing device 00771600122300000</t>
+          <t>Anti-crushing device 00771600122300000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -11789,25 +11773,21 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1040201904</t>
+          <t>1040201860</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Nut M5-8</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>GB/T889.1</t>
-        </is>
-      </c>
+          <t>Nut</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Chain System 00773700700000001; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -11819,25 +11799,25 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1040202297</t>
+          <t>1040201896</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Nut M16×1.5-10(Spiralock)</t>
+          <t>Nut M6-8</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>GB/T6177.2</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Anti-crushing device 00771600122300000</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -11849,21 +11829,25 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1040202854</t>
+          <t>1040201904</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Nut M6-8</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>Nut M5-8</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>GB/T889.1</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Chain System 00773700700000001; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -11875,21 +11859,25 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1040202855</t>
+          <t>1040202297</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Nut</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>Nut M16×1.5-10(Spiralock)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>GB/T6177.2</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -11901,15 +11889,15 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1040202861</t>
+          <t>1040202854</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Nut M12-10</t>
+          <t>Nut M6-8</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -11927,25 +11915,21 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1040300186</t>
+          <t>1040202855</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Washer</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>GB/T1230</t>
-        </is>
-      </c>
+          <t>Nut</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Rotary Mechanism 00773700900000000</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -11957,25 +11941,21 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1040300247</t>
+          <t>1040202861</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Washer 16-200HV</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>GB/T96.1</t>
-        </is>
-      </c>
+          <t>Nut M12-10</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -11987,7 +11967,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1040300514</t>
+          <t>1040300186</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -11995,17 +11975,17 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Washer 5-200HV</t>
+          <t>Washer</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T1230</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Chain System 00773700700000001</t>
+          <t>Rotary Mechanism 00773700900000000</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -12017,15 +11997,15 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1040300735</t>
+          <t>1040300247</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Washer 6-200HV</t>
+          <t>Washer 16-200HV</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -12035,7 +12015,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000; Chassis 02564702800000002</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -12047,15 +12027,15 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1040300771</t>
+          <t>1040300514</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Washer 6-200HV</t>
+          <t>Washer 5-200HV</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -12065,7 +12045,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Anti-crushing device 00771600122300000; Boom Assembly 02564700300000001; Hood 00773701130000000; Chassis 02564702800000002</t>
+          <t>Work Platform 00773600100000003 Standard; Chain System 00773700700000001</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -12077,25 +12057,25 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1040301033</t>
+          <t>1040300735</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Washer 20-300HV</t>
+          <t>Washer 6-200HV</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T96.1</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Anti-crushing device 00771600122300000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -12107,25 +12087,25 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1040301502</t>
+          <t>1040300771</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Washer 10-200HV; Washer</t>
+          <t>Washer 6-200HV</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>GB/T93</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Well-matched Rotary Centre Connector Installation 00773705212200000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Anti-crushing device 00771600122300000; Boom Assembly 02564700300000001; Hood 00773701130000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -12137,25 +12117,25 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1040301510</t>
+          <t>1040301033</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Washer 8; Washer 8-200HV; Washer8</t>
+          <t>Washer 20-300HV</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>GB/T93; GB/T93-</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Jib 00773700200000002; Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000; Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000; Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000; Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -12167,25 +12147,25 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1040301511</t>
+          <t>1040301502</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Washer 24-200HV</t>
+          <t>Washer 10-200HV; Washer</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T93</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Well-matched Rotary Centre Connector Installation 00773705212200000</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -12197,25 +12177,25 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1040301515</t>
+          <t>1040301510</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Washer 8-200HV; Washer    8-200HV</t>
+          <t>Washer 8; Washer 8-200HV; Washer8</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T93; GB/T93-</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Jib 00773700200000002; Boom Assembly 02564700300000001; Chain System 00773700700000001; Boom Assembly 02564700400000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Hood 00773701130000000; Chassis 02564702800000002</t>
+          <t>Jib 00773700200000002; Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000; Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000; Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000; Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -12227,25 +12207,25 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1040301610</t>
+          <t>1040301511</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Washer6</t>
+          <t>Washer 24-200HV</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>GB/T93-1987</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -12257,15 +12237,15 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1040302410</t>
+          <t>1040301515</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Washer 4-200HV</t>
+          <t>Washer 8-200HV; Washer    8-200HV</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -12275,7 +12255,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Jib 00773700200000002; Boom Assembly 02564700300000001; Chain System 00773700700000001; Boom Assembly 02564700400000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Hood 00773701130000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -12287,25 +12267,25 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>1040302480</t>
+          <t>1040301610</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Washer 8-200HV</t>
+          <t>Washer6</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>GB/T96.1</t>
+          <t>GB/T93-1987</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chain System 00773700700000001; Hood 00773701130000000</t>
+          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -12317,15 +12297,15 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1040302489</t>
+          <t>1040302410</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Washer 10-200HV; Washer    10-200HV; Washer10</t>
+          <t>Washer 4-200HV</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -12335,7 +12315,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001; Turntable 0773700860000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard); Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
+          <t>Anti-crushing device 00771600122300000</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -12347,25 +12327,25 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1040302490</t>
+          <t>1040302480</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Washer 12-200HV</t>
+          <t>Washer 8-200HV</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T96.1</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Boom Assembly 02564700300000001; Boom Assembly 02564700400000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Chain System 00773700700000001; Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -12377,15 +12357,15 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1040302492</t>
+          <t>1040302489</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Washer 16-200HV</t>
+          <t>Washer 10-200HV; Washer    10-200HV; Washer10</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -12395,7 +12375,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700300000001; Turntable 0773700860000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard); Rotary Mechanism Assembly Installation (Slewing) 00773700861000000 (Standard); Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -12407,25 +12387,25 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1040302512</t>
+          <t>1040302490</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Washer 10-200HV; Washer    10-200HV</t>
+          <t>Washer 12-200HV</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>GB/T96.1</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Hood 00773701130000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Boom Assembly 02564700300000001; Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -12437,25 +12417,25 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1040302529</t>
+          <t>1040302492</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Washer 5-200HV</t>
+          <t>Washer 16-200HV</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>GB/T96.1</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700400000000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -12467,21 +12447,25 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1040303520</t>
+          <t>1040302512</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Washer</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr"/>
+          <t>Washer 10-200HV; Washer    10-200HV</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>GB/T96.1</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Counterweight 00773701040000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option; Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -12493,21 +12477,25 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1040303579</t>
+          <t>1040302529</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Washer 6-200HV</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr"/>
+          <t>Washer 5-200HV</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>GB/T96.1</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Boom Assembly 02564700300000001</t>
+          <t>Boom Assembly 02564700400000000</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -12519,11 +12507,11 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040303579 </t>
+          <t>1040303520</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -12533,7 +12521,7 @@
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000</t>
+          <t>Counterweight 00773701040000000</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -12545,21 +12533,21 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1040303580</t>
+          <t>1040303579</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Washer</t>
+          <t>Washer 6-200HV</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000; Chassis 02564702800000002</t>
+          <t>Boom Assembly 02564700300000001</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -12571,11 +12559,11 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>1040303581</t>
+          <t>1040303579 10</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -12585,7 +12573,7 @@
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Turntable 0773700860000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
+          <t>Turntable 0773700860000000</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -12597,21 +12585,21 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1054600077</t>
+          <t>1040303580</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Needle bearing</t>
+          <t>Washer</t>
         </is>
       </c>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Turntable 0773700860000000; Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -12623,21 +12611,21 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1080000005</t>
+          <t>1040303581</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Oil cup M6×1</t>
+          <t>Washer</t>
         </is>
       </c>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
+          <t>Turntable 0773700860000000; Rotary Mechanism Assembly (Non fully slewing) 00773700861600000 (Standard)</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -12649,21 +12637,21 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1100700163</t>
+          <t>1054600077</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Door handle</t>
+          <t>Needle bearing</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -12675,21 +12663,21 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1101000163</t>
+          <t>1080000005</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Spring hinge</t>
+          <t>Oil cup M6×1</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Work Platform 00773600100000003 Standard</t>
+          <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -12701,21 +12689,21 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1101000180</t>
+          <t>1100700163</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>lock</t>
+          <t>Door handle</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Chassis 02564702800000002</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -12727,21 +12715,21 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1109900765</t>
+          <t>1101000163</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Hydraulic door lock</t>
+          <t>Spring hinge</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Work Platform 00773600100000003 Standard</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -12753,21 +12741,21 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1109900766</t>
+          <t>1101000180</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Battery gate lock</t>
+          <t>lock</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Chassis 02564702800000002</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -12779,7 +12767,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>1109900986</t>
+          <t>1109900765</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -12787,13 +12775,13 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Chain connector I E4.421.12.1.1</t>
+          <t>Hydraulic door lock</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Chain System 00773700700000001</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -12805,7 +12793,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1109900987</t>
+          <t>1109900766</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -12813,13 +12801,13 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Chain connector II E4.421.12.1.2</t>
+          <t>Battery gate lock</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Chain System 00773700700000001</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -12831,15 +12819,15 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1109900988</t>
+          <t>1109900986</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Chain side plate (outside) E4.42.01</t>
+          <t>Chain connector I E4.421.12.1.1</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
@@ -12857,15 +12845,15 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>1109900990</t>
+          <t>1109900987</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Chain side plate (inside) E4.42.02.075.0</t>
+          <t>Chain connector II E4.421.12.1.2</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -12883,15 +12871,15 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>1109900991</t>
+          <t>1109900988</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Chain cross-bar 385.12</t>
+          <t>Chain side plate (outside) E4.42.01</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
@@ -12909,7 +12897,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1109900993</t>
+          <t>1109900990</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -12917,7 +12905,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Chain shim 42.1</t>
+          <t>Chain side plate (inside) E4.42.02.075.0</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
@@ -12935,21 +12923,21 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>1110100355</t>
+          <t>1109900991</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Gas spring</t>
+          <t>Chain cross-bar 385.12</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Hood 00773701130000000</t>
+          <t>Chain System 00773700700000001</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -12961,25 +12949,21 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>1140101461</t>
+          <t>1109900993</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>2 pieces/Unit</t>
-        </is>
-      </c>
+          <t>Chain shim 42.1</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000; Left-Right Steering Cylinder Connector Assembly 00773702801400000</t>
+          <t>Chain System 00773700700000001</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -12991,21 +12975,21 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>1140101462</t>
+          <t>1110100355</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Gas spring</t>
         </is>
       </c>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
+          <t>Hood 00773701130000000</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -13017,21 +13001,25 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>1140101463</t>
+          <t>1140101461</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
           <t>Male stud connector</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>2 pieces/Unit</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000; Left-Right Steering Cylinder Connector Assembly 00773702801400000</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -13043,11 +13031,11 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>1140101464</t>
+          <t>1140101462</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -13057,7 +13045,7 @@
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Upper Boom Hydraulic Components - Lifting Balance Valve Installation 00773705200800000</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -13069,11 +13057,11 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>1140101465</t>
+          <t>1140101463</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -13083,7 +13071,7 @@
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Upper Boom Hydraulic Components - Telescopic Balance Valve Installation 00773705210800000</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -13095,21 +13083,21 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1140101475</t>
+          <t>1140101464</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Tube to bend; Male stud connector</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -13121,21 +13109,21 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>1140101476</t>
+          <t>1140101465</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Tube to bend; Combined connector</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -13147,21 +13135,21 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>1140101477</t>
+          <t>1140101475</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Combined connector; Tube to bend; Male stud connector</t>
+          <t>Tube to bend; Male stud connector</t>
         </is>
       </c>
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000</t>
+          <t>Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -13173,21 +13161,21 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>1140101478</t>
+          <t>1140101476</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Combined connector; Tube to bend</t>
+          <t>Tube to bend; Combined connector</t>
         </is>
       </c>
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000; Well-matched Rotary Centre Connector Installation 00773705212200000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -13199,21 +13187,21 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1140101483</t>
+          <t>1140101477</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Combined connector; Tube to bend; Male stud connector</t>
         </is>
       </c>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000</t>
+          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000; Turntable Hydraulic Components - High Pressure Filter Assembly 02564705210400000; Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -13225,21 +13213,21 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1140101487</t>
+          <t>1140101478</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Combined connector; Tube to bend</t>
         </is>
       </c>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Left-Right Float Cylinder Connector Assembly 00773702803000000</t>
+          <t>Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000; Well-matched Rotary Centre Connector Installation 00773705212200000</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -13251,7 +13239,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1140101489</t>
+          <t>1140101483</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -13265,7 +13253,7 @@
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -13277,21 +13265,21 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>1140101521</t>
+          <t>1140101487</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000</t>
+          <t>Left-Right Float Cylinder Connector Assembly 00773702803000000</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -13303,7 +13291,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1140101629</t>
+          <t>1140101489</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -13311,13 +13299,13 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Plug</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -13329,21 +13317,21 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1140101737</t>
+          <t>1140101521</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Combined connector</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Chassis Hydraulic Components - Emergency Pump Assembly 02564705220200000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -13355,25 +13343,21 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>1140101793</t>
+          <t>1140101629</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>2 pieces/Unit</t>
-        </is>
-      </c>
+          <t>Plug</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Left-Right Steering Cylinder Connector Assembly 00773702801400000</t>
+          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -13385,21 +13369,21 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>1140101809</t>
+          <t>1140101737</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Reducer union; Tube to reducer union</t>
+          <t>Combined connector</t>
         </is>
       </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -13411,7 +13395,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1140101827</t>
+          <t>1140101793</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -13419,13 +13403,17 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Combined connector</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr"/>
+          <t>Tube to swivel</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2 pieces/Unit</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
+          <t>Left-Right Steering Cylinder Connector Assembly 00773702801400000</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -13437,21 +13425,21 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1140101941</t>
+          <t>1140101809</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Reducer union; Tube to reducer union</t>
         </is>
       </c>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -13463,21 +13451,21 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1140102940</t>
+          <t>1140101827</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Combined connector</t>
         </is>
       </c>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -13489,25 +13477,21 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>1140103526</t>
+          <t>1140101941</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Articulating connector</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>2 pieces/Unit</t>
-        </is>
-      </c>
+          <t>Male stud connector</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Left-Right Steering Cylinder Connector Assembly 00773702801400000</t>
+          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -13519,21 +13503,21 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>1140107397</t>
+          <t>1140102940</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000; Chassis Hydraulic Components - Gear Pump Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -13545,21 +13529,25 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>1140107416</t>
+          <t>1140103526</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Plug</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr"/>
+          <t>Articulating connector</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2 pieces/Unit</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Left-Right Steering Cylinder Connector Assembly 00773702801400000</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -13571,21 +13559,21 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1140111237</t>
+          <t>1140107397</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -13597,21 +13585,21 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>1140111291</t>
+          <t>1140107416</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Plug</t>
         </is>
       </c>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -13623,7 +13611,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>1140113796</t>
+          <t>1140111237</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -13631,13 +13619,13 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>45° combined connector; 45°combined bend</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000; Tower Boom Hydraulic Components - Right Cylinder Control Valve 00773705200600000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -13649,7 +13637,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1140114187</t>
+          <t>1140111291</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -13657,13 +13645,13 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Pressure test connector; Pressure testing connector</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -13675,21 +13663,21 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>1140114451</t>
+          <t>1140113796</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>45°combined bend</t>
+          <t>45° combined connector; 45°combined bend</t>
         </is>
       </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -13701,21 +13689,21 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1140114591</t>
+          <t>1140114187</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Tube to reducer union</t>
+          <t>Pressure test connector; Pressure testing connector</t>
         </is>
       </c>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -13727,21 +13715,21 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>1140114620</t>
+          <t>1140114451</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>45°combined bend</t>
         </is>
       </c>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Turntable Hydraulic Components - Main Valve Assembly 02564705210400000</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -13753,7 +13741,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1140114625</t>
+          <t>1140114591</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -13761,13 +13749,13 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Tube to reducer union</t>
         </is>
       </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
+          <t>Chassis Hydraulic Components - Hydraulic Tank Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -13779,11 +13767,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>1140114647</t>
+          <t>1140114620</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -13793,7 +13781,7 @@
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Left-Right Float Cylinder Connector Assembly 00773702803000000</t>
+          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000; Turntable Hydraulic Components - Leveling Selective Valve Assembly 02564705210400000; Turntable Hydraulic Components - Overflow Hydraulic Lock Assembly 02564705210400000; Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -13805,7 +13793,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>1140114698</t>
+          <t>1140114625</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -13819,7 +13807,7 @@
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Well-matched Rotary Centre Connector Installation 00773705212200000</t>
+          <t>Chassis Hydraulic Components - Float Balance Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -13831,7 +13819,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1140114700</t>
+          <t>1140114647</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -13845,7 +13833,7 @@
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000</t>
+          <t>Left-Right Float Cylinder Connector Assembly 00773702803000000</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -13857,21 +13845,21 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1140114839</t>
+          <t>1140114698</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Articulating connector</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
+          <t>Well-matched Rotary Centre Connector Installation 00773705212200000</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -13883,11 +13871,11 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>1140114948</t>
+          <t>1140114700</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -13897,7 +13885,7 @@
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
+          <t>Upper Boom Hydraulic Components - Upper Leveling Cylinder Valve Installation 00773705210800000</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -13909,21 +13897,21 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>1140115519</t>
+          <t>1140114839</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Articulating connector</t>
         </is>
       </c>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000</t>
+          <t>Jib Hydraulic Components Cylinder CBV Assembly 00773705211000000</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -13935,11 +13923,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>1140252472</t>
+          <t>1140114948</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -13949,7 +13937,7 @@
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Well-matched Rotary Centre Connector Installation 00773705212200000</t>
+          <t>Platform Hydraulic Components - Platform Select Valve Installation 00773705211200000</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -13961,11 +13949,11 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1149901685</t>
+          <t>1140115519</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
@@ -13975,7 +13963,7 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000</t>
+          <t>Chassis Hydraulic Components - Steering Priority Valve Assembly 02564705220200000</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -13987,21 +13975,21 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1159901036</t>
+          <t>1140252472</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Spring hinge</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Anti-crushing device 00771600122300000</t>
+          <t>Well-matched Rotary Centre Connector Installation 00773705212200000</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -14013,7 +14001,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1999904986</t>
+          <t>1149901685</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -14021,16 +14009,68 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Document box 355×280×55</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
+          <t>Chassis Hydraulic Components - Float Control Valve Assembly 02564705220200000; Tower Boom Hydraulic Components - Left Cylinder Control Valve Installation 00773705200600000</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>ZA20JERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>1159901036</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>2</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Spring hinge</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Anti-crushing device 00771600122300000</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>ZA20JERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>1999904986</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>2</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Document box 355×280×55</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
+      <c r="E505" t="inlineStr">
+        <is>
           <t>Work Platform 00773600100000003 Standard; Work Platform 00774000120000002 Option</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr">
+      <c r="F505" t="inlineStr">
         <is>
           <t>ZA20JERT</t>
         </is>
